--- a/TestData/UploadFiles/RequestBody.xlsx
+++ b/TestData/UploadFiles/RequestBody.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView windowWidth="28800" windowHeight="12180" firstSheet="0" activeTab="0"/>
+    <x:workbookView windowWidth="28800" windowHeight="12180" firstSheet="0" activeTab="9"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="register_Body" sheetId="1" r:id="rId1"/>
@@ -12,13 +12,14 @@
     <x:sheet name="login_body" sheetId="3" r:id="rId3"/>
     <x:sheet name="getExistingUser" sheetId="4" r:id="rId4"/>
     <x:sheet name="Body_Response" sheetId="5" r:id="rId5"/>
-    <x:sheet name="patientGetFhirData_Body" sheetId="6" r:id="rId9"/>
-    <x:sheet name="patientUpdate_Body" sheetId="7" r:id="rId10"/>
-    <x:sheet name="patientFacesheet_Body" sheetId="8" r:id="rId11"/>
-    <x:sheet name="patientDelete_Body" sheetId="9" r:id="rId12"/>
-    <x:sheet name="patientBulkProviders_Body" sheetId="10" r:id="rId13"/>
-    <x:sheet name="patientEmrSearch_Body" sheetId="11" r:id="rId14"/>
-    <x:sheet name="patientEmrAddUpdate_Body" sheetId="12" r:id="rId15"/>
+    <x:sheet name="patientGetFhirData_Body" sheetId="6" r:id="rId6"/>
+    <x:sheet name="patientUpdate_Body" sheetId="7" r:id="rId7"/>
+    <x:sheet name="patientFacesheet_Body" sheetId="8" r:id="rId8"/>
+    <x:sheet name="patientDelete_Body" sheetId="9" r:id="rId9"/>
+    <x:sheet name="patientBulkProviders_Body" sheetId="10" r:id="rId10"/>
+    <x:sheet name="patientEmrSearch_Body" sheetId="11" r:id="rId11"/>
+    <x:sheet name="patientEmrAddUpdate_Body" sheetId="12" r:id="rId12"/>
+    <x:sheet name="patientList_Body" sheetId="13" r:id="rId13"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="191029"/>
@@ -171,6 +172,9 @@
   </x:si>
   <x:si>
     <x:t>{"firstName":"Test","lastName":"Patient","dateOfBirth":"1990-01-01","gender":"Unknown"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"BusinessUnitIds":["{{BusinessUnitId}}"],"PatientVisibilityInDays":30,"Status":"All","Mode":"Recent","Insurance":"All","PatientName":"","ServiceRequestedBy":"All","Offset":0,"Limit":25,"TrackedBy":"All","TagNames":[],"LastDurationOfRecords":"{{LastDurationOfRecords}}"}</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -797,8 +801,11 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,28 +858,9 @@
     <x:cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <x:cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </x:cellStyles>
-  <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <x:tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <x:tableStyleElement type="wholeTable" dxfId="6"/>
-      <x:tableStyleElement type="headerRow" dxfId="5"/>
-      <x:tableStyleElement type="totalRow" dxfId="4"/>
-      <x:tableStyleElement type="firstColumn" dxfId="3"/>
-      <x:tableStyleElement type="lastColumn" dxfId="2"/>
-      <x:tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <x:tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </x:tableStyle>
-    <x:tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <x:tableStyleElement type="headerRow" dxfId="16"/>
-      <x:tableStyleElement type="totalRow" dxfId="15"/>
-      <x:tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <x:tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <x:tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <x:tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <x:tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <x:tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <x:tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <x:tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </x:tableStyle>
+  <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
+    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{0B412F67-EE37-4DE5-A33D-BF0119E27FC8}"/>
+    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{20E22920-9214-4445-BDE7-528042BFBF79}"/>
   </x:tableStyles>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1266,12 +1254,12 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1292,19 +1280,19 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1325,19 +1313,19 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1358,7 +1346,44 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B2"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="132" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2" ht="86" customHeight="1">
+      <x:c r="A2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
@@ -1551,12 +1576,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1577,19 +1602,19 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1610,19 +1635,19 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1643,19 +1668,19 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1676,7 +1701,7 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>

--- a/TestData/UploadFiles/RequestBody.xlsx
+++ b/TestData/UploadFiles/RequestBody.xlsx
@@ -20,6 +20,9 @@
     <x:sheet name="patientEmrSearch_Body" sheetId="11" r:id="rId11"/>
     <x:sheet name="patientEmrAddUpdate_Body" sheetId="12" r:id="rId12"/>
     <x:sheet name="patientList_Body" sheetId="13" r:id="rId13"/>
+    <x:sheet name="patientGetFeatureBasedData_Body" sheetId="14" r:id="rId17"/>
+    <x:sheet name="patientSearch_Body" sheetId="15" r:id="rId18"/>
+    <x:sheet name="patientSearch_Filter" sheetId="16" r:id="rId19"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="191029"/>
@@ -153,7 +156,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>{"businessUnitIds":["67793c57-831f-11ea-bd7d-04d9f5ab62dc"],"currentBusinessUnitId":"67793c57-831f-11ea-bd7d-04d9f5ab62dc"}</x:t>
+    <x:t>{"businessUnitIds":["{{BusinessUnitId}}"],"currentBusinessUnitId":"{{BusinessUnitId}}"}</x:t>
   </x:si>
   <x:si>
     <x:t>{"firstName":"SecurityTest","lastName":"Patient"}</x:t>
@@ -175,6 +178,24 @@
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitIds":["{{BusinessUnitId}}"],"PatientVisibilityInDays":30,"Status":"All","Mode":"Recent","Insurance":"All","PatientName":"","ServiceRequestedBy":"All","Offset":0,"Limit":25,"TrackedBy":"All","TagNames":[],"LastDurationOfRecords":"{{LastDurationOfRecords}}"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"PatientDemographic":{"Filter":{"BusinessUnitId":"{{BusinessUnitId}}","Limit":10}},"AllergyIntolerance":{"FilterModel":{"BusinessUnitId":"{{BusinessUnitId}}","Limit":10}},"Condition":{"Filter":{"BusinessUnitId":"{{BusinessUnitId}}","Limit":10}},"Coverage":{"Filter":{"BusinessUnitId":"{{BusinessUnitId}}","Limit":10}},"Immunization":{"Filter":{"BusinessUnitId":"{{BusinessUnitId}}","Limit":10}},"MedicationRequest":{"Filter":{"BusinessUnitId":"{{BusinessUnitId}}","Limit":10}},"ProgressNote":{"Filter":{"BusinessUnitId":"{{BusinessUnitId}}","Limit":10,"ShowAllProgressNotes":false},"Output":{"ProgressNote":true}}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"Insurance":"{{Insurance}}","Mode":"{{Sort}}","OrderBy":"{{By}}","PatientDemographic":{"Filter":{"Ssn":[null],"Dob":["{{Dob}}"],"FirstName":["{{FirstName}}"],"LastName":["{{LastName}}"],"Gender":[null],"Zipcode":[],"StreetAddress":[],"City":[],"Email":[],"Phone":[],"InsuranceId":[],"InsuranceName":[]}}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>First Fax</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Iverson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dob</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-01-1960</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1389,6 +1410,121 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B2"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B2"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:B1"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:2">
+      <x:c r="A1" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:2">
+      <x:c r="A3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2">
+      <x:c r="A4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>

--- a/TestData/UploadFiles/RequestBody.xlsx
+++ b/TestData/UploadFiles/RequestBody.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView windowWidth="28800" windowHeight="12180" firstSheet="0" activeTab="9"/>
+    <x:workbookView windowWidth="28800" windowHeight="12180" firstSheet="0" activeTab="14"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="register_Body" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,9 @@
     <x:sheet name="patientEmrSearch_Body" sheetId="11" r:id="rId11"/>
     <x:sheet name="patientEmrAddUpdate_Body" sheetId="12" r:id="rId12"/>
     <x:sheet name="patientList_Body" sheetId="13" r:id="rId13"/>
-    <x:sheet name="patientGetFeatureBasedData_Body" sheetId="14" r:id="rId17"/>
-    <x:sheet name="patientSearch_Body" sheetId="15" r:id="rId18"/>
-    <x:sheet name="patientSearch_Filter" sheetId="16" r:id="rId19"/>
+    <x:sheet name="patientGetFeatureBasedData_Body" sheetId="14" r:id="rId14"/>
+    <x:sheet name="patientSearch_Body" sheetId="15" r:id="rId15"/>
+    <x:sheet name="patientSearch_Filter" sheetId="16" r:id="rId16"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="191029"/>
@@ -880,8 +880,8 @@
     <x:cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </x:cellStyles>
   <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{0B412F67-EE37-4DE5-A33D-BF0119E27FC8}"/>
-    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{20E22920-9214-4445-BDE7-528042BFBF79}"/>
+    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{60CBAA0B-D873-4829-8042-76E981052673}"/>
+    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{7B0AB8B5-2AD2-4A72-9D63-91A426D5047E}"/>
   </x:tableStyles>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1381,7 +1381,7 @@
   <x:dimension ref="A1:B2"/>
   <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="132" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1411,12 +1411,12 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1437,19 +1437,23 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="255" style="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1470,19 +1474,19 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:dimension ref="A1:B4"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -1519,7 +1523,7 @@
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
